--- a/BeatnotePostCombFix/Apr06,2026/April6_OlderFits_VaryGamma.xlsx
+++ b/BeatnotePostCombFix/Apr06,2026/April6_OlderFits_VaryGamma.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostCombFix\Apr06,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39F46B65-9B85-4812-8C7C-F09DF0B1DB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC03487-A0AF-418F-B152-9D542EA7E835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{DE27D4D9-8A5E-4A81-9645-FB782B2C9508}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{DE27D4D9-8A5E-4A81-9645-FB782B2C9508}"/>
   </bookViews>
   <sheets>
     <sheet name="456" sheetId="1" r:id="rId1"/>
@@ -3788,16 +3788,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>282575</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>358775</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>53975</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>339725</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3824,16 +3824,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>447675</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>60325</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>41275</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>549275</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>41275</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>346075</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4976,27 +4976,27 @@
         <v>9.6088335511934186</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:Q3" si="0">AVERAGE(C2:C8,C9:C15)</f>
+        <f>AVERAGE(C2:C8,C9:C15)</f>
         <v>1.1621065158458728</v>
       </c>
       <c r="M3">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(D2:D8,D9:D15)</f>
         <v>-1.5775610011044422E-3</v>
       </c>
       <c r="N3">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(E2:E8,E9:E15)</f>
         <v>2.6608353107389324</v>
       </c>
       <c r="O3">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(F2:F8,F9:F15)</f>
         <v>41.906194637181123</v>
       </c>
       <c r="P3">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(G2:G8,G9:G15)</f>
         <v>2.2966578140585538E-3</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="0"/>
+        <f>AVERAGE(H2:H8,H9:H15)</f>
         <v>3.9720000673721056E-2</v>
       </c>
     </row>
@@ -5037,23 +5037,23 @@
         <v>5.252449588536383E-3</v>
       </c>
       <c r="M4">
-        <f t="shared" ref="M4:Q4" si="1">_xlfn.STDEV.S(D2:D8,D9:D15)</f>
+        <f>_xlfn.STDEV.S(D2:D8,D9:D15)</f>
         <v>9.143262698338931E-4</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
+        <f>_xlfn.STDEV.S(E2:E8,E9:E15)</f>
         <v>0.47761766086667917</v>
       </c>
       <c r="O4">
-        <f t="shared" si="1"/>
+        <f>_xlfn.STDEV.S(F2:F8,F9:F15)</f>
         <v>1.0820372207622722</v>
       </c>
       <c r="P4">
-        <f t="shared" si="1"/>
+        <f>_xlfn.STDEV.S(G2:G8,G9:G15)</f>
         <v>2.1205116713350879E-5</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="1"/>
+        <f>_xlfn.STDEV.S(H2:H8,H9:H15)</f>
         <v>8.6279095495304925E-4</v>
       </c>
     </row>
@@ -5124,19 +5124,19 @@
         <v>-57.958219631049325</v>
       </c>
       <c r="N6">
-        <f t="shared" ref="N6:Q6" si="2">N4/N3*100</f>
+        <f t="shared" ref="N6:Q6" si="0">N4/N3*100</f>
         <v>17.949914409924205</v>
       </c>
       <c r="O6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.582045996135947</v>
       </c>
       <c r="P6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>0.92330327067218254</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2.1721826292009001</v>
       </c>
     </row>

--- a/BeatnotePostCombFix/Apr06,2026/April6_OlderFits_VaryGamma.xlsx
+++ b/BeatnotePostCombFix/Apr06,2026/April6_OlderFits_VaryGamma.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wolfwalker\Documents\git\6s7p\BeatnotePostCombFix\Apr06,2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Diego\git\6s7p\BeatnotePostCombFix\Apr06,2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC03487-A0AF-418F-B152-9D542EA7E835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DBC7E5-8290-403C-B018-08233A5CE94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{DE27D4D9-8A5E-4A81-9645-FB782B2C9508}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DE27D4D9-8A5E-4A81-9645-FB782B2C9508}"/>
   </bookViews>
   <sheets>
     <sheet name="456" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -128,7 +131,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,7 +482,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -487,6 +489,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -803,7 +806,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -811,6 +813,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1122,7 +1125,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1130,6 +1132,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1441,7 +1444,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1449,6 +1451,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3711,16 +3714,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>522123</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>174186</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>118710</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>331069</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>394685</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>250387</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>56028</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>403412</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3747,16 +3750,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>43793</xdr:colOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>174788</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>204952</xdr:rowOff>
+      <xdr:rowOff>348695</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>354724</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>486104</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>189186</xdr:rowOff>
+      <xdr:rowOff>332929</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3788,16 +3791,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>34925</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>244475</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>15875</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>225425</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4179,12 +4182,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89E67E67-BE51-40B6-BF6A-AB076C1A076C}">
   <dimension ref="A1:Q19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="10" max="10" width="10.36328125" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4210,7 +4213,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4257,7 +4260,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -4318,7 +4321,7 @@
         <v>6.7196783564735787E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -4379,7 +4382,7 @@
         <v>8.7450229714018397E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4405,7 +4408,7 @@
         <v>6.0223458005847002E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -4466,7 +4469,7 @@
         <v>13.014049940317593</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -4504,7 +4507,7 @@
         <v>5.7857693431690902E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -4530,7 +4533,7 @@
         <v>7.7968480004249902E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -4564,7 +4567,7 @@
         <v>1.2821354871451585</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -4594,7 +4597,7 @@
         <v>1.2642645622799633</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -4620,7 +4623,7 @@
         <v>7.8000210714507601E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -4650,7 +4653,7 @@
         <v>1.0027252673704417</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -4676,7 +4679,7 @@
         <v>6.3546524311469798E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
@@ -4706,7 +4709,7 @@
         <v>1.2004393355802754</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
@@ -4736,7 +4739,7 @@
         <v>1.1293578515144338</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="42.75">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
@@ -4766,7 +4769,7 @@
         <v>1.2004350253272649</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="42.75">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -4796,7 +4799,7 @@
         <v>1.4590292319728295</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="42.75">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
@@ -4826,7 +4829,7 @@
         <v>1.3431363218040231</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="42.75">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
@@ -4865,12 +4868,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6499FFC7-3DA5-4057-863B-C101A2BD7DDC}">
   <dimension ref="A1:Q15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="10" max="10" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4896,7 +4899,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="42.75">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -4943,7 +4946,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="42.75">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -4972,35 +4975,35 @@
         <v>26</v>
       </c>
       <c r="K3">
-        <f>AVERAGE(B2:B8,B9:B15)</f>
+        <f t="shared" ref="K3:Q3" si="0">AVERAGE(B2:B8,B9:B15)</f>
         <v>9.6088335511934186</v>
       </c>
       <c r="L3">
-        <f>AVERAGE(C2:C8,C9:C15)</f>
+        <f t="shared" si="0"/>
         <v>1.1621065158458728</v>
       </c>
       <c r="M3">
-        <f>AVERAGE(D2:D8,D9:D15)</f>
+        <f t="shared" si="0"/>
         <v>-1.5775610011044422E-3</v>
       </c>
       <c r="N3">
-        <f>AVERAGE(E2:E8,E9:E15)</f>
+        <f t="shared" si="0"/>
         <v>2.6608353107389324</v>
       </c>
       <c r="O3">
-        <f>AVERAGE(F2:F8,F9:F15)</f>
+        <f t="shared" si="0"/>
         <v>41.906194637181123</v>
       </c>
       <c r="P3">
-        <f>AVERAGE(G2:G8,G9:G15)</f>
+        <f t="shared" si="0"/>
         <v>2.2966578140585538E-3</v>
       </c>
       <c r="Q3">
-        <f>AVERAGE(H2:H8,H9:H15)</f>
+        <f t="shared" si="0"/>
         <v>3.9720000673721056E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="42.75">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -5029,35 +5032,35 @@
         <v>27</v>
       </c>
       <c r="K4">
-        <f>_xlfn.STDEV.S(B2:B8,B9:B15)</f>
+        <f t="shared" ref="K4:Q4" si="1">_xlfn.STDEV.S(B2:B8,B9:B15)</f>
         <v>7.7668592218918517E-2</v>
       </c>
       <c r="L4">
-        <f>_xlfn.STDEV.S(C2:C8,C9:C15)</f>
+        <f t="shared" si="1"/>
         <v>5.252449588536383E-3</v>
       </c>
       <c r="M4">
-        <f>_xlfn.STDEV.S(D2:D8,D9:D15)</f>
+        <f t="shared" si="1"/>
         <v>9.143262698338931E-4</v>
       </c>
       <c r="N4">
-        <f>_xlfn.STDEV.S(E2:E8,E9:E15)</f>
+        <f t="shared" si="1"/>
         <v>0.47761766086667917</v>
       </c>
       <c r="O4">
-        <f>_xlfn.STDEV.S(F2:F8,F9:F15)</f>
+        <f t="shared" si="1"/>
         <v>1.0820372207622722</v>
       </c>
       <c r="P4">
-        <f>_xlfn.STDEV.S(G2:G8,G9:G15)</f>
+        <f t="shared" si="1"/>
         <v>2.1205116713350879E-5</v>
       </c>
       <c r="Q4">
-        <f>_xlfn.STDEV.S(H2:H8,H9:H15)</f>
+        <f t="shared" si="1"/>
         <v>8.6279095495304925E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="42.75">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -5083,7 +5086,7 @@
         <v>3.8826109217313297E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="42.75">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -5124,23 +5127,23 @@
         <v>-57.958219631049325</v>
       </c>
       <c r="N6">
-        <f t="shared" ref="N6:Q6" si="0">N4/N3*100</f>
+        <f t="shared" ref="N6:Q6" si="2">N4/N3*100</f>
         <v>17.949914409924205</v>
       </c>
       <c r="O6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.582045996135947</v>
       </c>
       <c r="P6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.92330327067218254</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.1721826292009001</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" ht="42.75">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -5170,7 +5173,7 @@
         <v>0.19051909527002869</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="42.75">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -5196,7 +5199,7 @@
         <v>3.84086464084595E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="42.75">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -5222,7 +5225,7 @@
         <v>4.0270956489123703E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" ht="42.75">
       <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
@@ -5248,7 +5251,7 @@
         <v>4.0877162789576302E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="42.75">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -5278,7 +5281,7 @@
         <v>2.2879625685735773E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="42.75">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -5304,7 +5307,7 @@
         <v>4.02841943243843E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" ht="42.75">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -5334,7 +5337,7 @@
         <v>2.2873004957014078E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="42.75">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -5360,7 +5363,7 @@
         <v>3.9820041350796802E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="42.75">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
